--- a/data/trans_orig/IP2907_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46565</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77040</t>
+          <t>76741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83573</t>
+          <t>84121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>97792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81028</t>
+          <t>82411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109875</t>
+          <t>110415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171772</t>
+          <t>172071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202247</t>
+          <t>203058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32158</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54797</t>
+          <t>54029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60818</t>
+          <t>60275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89305</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143659</t>
+          <t>144458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160125</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190441</t>
+          <t>191209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213080</t>
+          <t>212951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340218</t>
+          <t>340977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368705</t>
+          <t>369248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47405</t>
+          <t>50271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52572</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80650</t>
+          <t>80602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118237</t>
+          <t>119118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136154</t>
+          <t>136864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133751</t>
+          <t>130885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156733</t>
+          <t>156441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259788</t>
+          <t>259836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287866</t>
+          <t>288275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>25104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>41547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22929</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77630</t>
+          <t>77713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117976</t>
+          <t>118837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135231</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134832</t>
+          <t>133718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152203</t>
+          <t>152255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257886</t>
+          <t>257803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>282261</t>
+          <t>282575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100877</t>
+          <t>100103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132963</t>
+          <t>135554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125043</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172695</t>
+          <t>171111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237069</t>
+          <t>236214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295702</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>484046</t>
+          <t>481455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>516132</t>
+          <t>516906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>564585</t>
+          <t>566169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>612237</t>
+          <t>610710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058587</t>
+          <t>1063608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1117220</t>
+          <t>1118075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2907_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30185</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20592</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39750</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21450</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15266</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28937</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53343</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59521</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>40956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76741</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>91710</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82145</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>101303</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>91608</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84121</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>97792</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97683</t>
+          <t>94891</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82411</t>
+          <t>87875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>101122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>189291</t>
+          <t>186601</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172071</t>
+          <t>173795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203058</t>
+          <t>197684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121895</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121895</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121895</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135754</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135754</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135754</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>248812</t>
+          <t>238640</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>248812</t>
+          <t>238640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>248812</t>
+          <t>238640</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38593</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29407</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49462</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31785</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24285</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39827</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>22550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54029</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>74008</t>
+          <t>68693</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60275</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>83278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>190326</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>179457</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>199512</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>152500</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>144458</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>203015</t>
+          <t>148480</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191209</t>
+          <t>139887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212951</t>
+          <t>156030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>355515</t>
+          <t>338806</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340977</t>
+          <t>324221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369248</t>
+          <t>350316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>228919</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>228919</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>228919</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>184285</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>184285</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>184285</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>245238</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245238</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>245238</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>429523</t>
+          <t>407499</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>429523</t>
+          <t>407499</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>429523</t>
+          <t>407499</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32598</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23444</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46492</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30950</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22418</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>40164</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50271</t>
+          <t>40348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65307</t>
+          <t>63706</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52163</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132059</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>118165</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141213</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>128332</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119118</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136864</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146799</t>
+          <t>119012</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130885</t>
+          <t>109772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156441</t>
+          <t>126754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>275131</t>
+          <t>251071</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259836</t>
+          <t>236872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288275</t>
+          <t>263414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>159282</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>159282</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>159282</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150120</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>340438</t>
+          <t>314777</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340438</t>
+          <t>314777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>340438</t>
+          <t>314777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29373</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21303</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38429</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33241</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25104</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41547</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52941</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77713</t>
+          <t>75541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134737</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>125681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142807</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>127143</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>118837</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>135280</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>126513</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133718</t>
+          <t>117649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152255</t>
+          <t>134706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>271019</t>
+          <t>261249</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257803</t>
+          <t>248224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>282575</t>
+          <t>273228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>130749</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>111678</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>150256</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>117425</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100103</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>135554</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126570</t>
+          <t>101842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171111</t>
+          <t>133829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236214</t>
+          <t>223274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>276884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>548832</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>529325</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>567903</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>499584</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>481455</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>516906</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>591373</t>
+          <t>488895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>566169</t>
+          <t>471271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>610710</t>
+          <t>503258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1090957</t>
+          <t>1037727</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1063608</t>
+          <t>1007797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1118075</t>
+          <t>1061407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
